--- a/results/case_0001/optimized_results.xlsx
+++ b/results/case_0001/optimized_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:AF4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,25 +499,80 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>long_provided_mm2</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>VRebar_req</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>TTrnRebar_req</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>TLngRebar_req</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>VRebar_req_units</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>TTrnRebar_req_units</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>TLngRebar_req_units</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>check_torsion</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>check_shear</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>check_longitudinal</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>check_detailing</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>transverse_weight_kg_per_m</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>longitudinal_weight_kg_per_m</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>total_weight_kg_per_m</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>evaluated_candidates</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>feasible_candidates</t>
         </is>
@@ -595,18 +650,57 @@
         <v>14</v>
       </c>
       <c r="Q2" t="n">
+        <v>2786</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1492.33</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1115.53</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2727</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>mm2/m</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>mm2/m</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>mm2</t>
+        </is>
+      </c>
+      <c r="X2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
         <v>25.66636</v>
       </c>
-      <c r="R2" t="n">
+      <c r="AC2" t="n">
         <v>21.8701</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AD2" t="n">
         <v>47.53645999999999</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AE2" t="n">
         <v>4800</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AF2" t="n">
         <v>4297</v>
       </c>
     </row>
@@ -682,18 +776,57 @@
         <v>14</v>
       </c>
       <c r="Q3" t="n">
+        <v>1806</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1495.83</v>
+      </c>
+      <c r="S3" t="n">
+        <v>685.65</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1721</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>mm2/m</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>mm2/m</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>mm2</t>
+        </is>
+      </c>
+      <c r="X3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
         <v>18.84174444444444</v>
       </c>
-      <c r="R3" t="n">
+      <c r="AC3" t="n">
         <v>14.1771</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AD3" t="n">
         <v>33.01884444444444</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AE3" t="n">
         <v>4800</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AF3" t="n">
         <v>4271</v>
       </c>
     </row>
@@ -769,18 +902,57 @@
         <v>10</v>
       </c>
       <c r="Q4" t="n">
+        <v>1990</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2086.39</v>
+      </c>
+      <c r="S4" t="n">
+        <v>784.53</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1918</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>mm2/m</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>mm2/m</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>mm2</t>
+        </is>
+      </c>
+      <c r="X4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
         <v>23.43561428571428</v>
       </c>
-      <c r="R4" t="n">
+      <c r="AC4" t="n">
         <v>15.6215</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AD4" t="n">
         <v>39.05711428571428</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AE4" t="n">
         <v>4800</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AF4" t="n">
         <v>4298</v>
       </c>
     </row>
